--- a/data/trans_orig/IP07A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A05-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24924</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>33500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>49016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31874</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>39184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54242</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70585</t>
+          <t>71132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93472</t>
+          <t>93594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77282</t>
+          <t>77380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101053</t>
+          <t>101619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157077</t>
+          <t>154744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188133</t>
+          <t>188719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87628</t>
+          <t>86298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109218</t>
+          <t>109029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110532</t>
+          <t>111036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134890</t>
+          <t>135334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>203613</t>
+          <t>201729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236409</t>
+          <t>238959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27750</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>31051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34441</t>
+          <t>34642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53922</t>
+          <t>55432</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>34596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>43592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>60869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43867</t>
+          <t>44157</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21557</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34082</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56640</t>
+          <t>56457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74848</t>
+          <t>73986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>111968</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>139968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125323</t>
+          <t>125772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246176</t>
+          <t>245938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>286825</t>
+          <t>285827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>147848</t>
+          <t>146931</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177700</t>
+          <t>177254</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>155550</t>
+          <t>156254</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184939</t>
+          <t>184719</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>312506</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>353106</t>
+          <t>352604</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47586</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71228</t>
+          <t>71262</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>34406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>38510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50479</t>
+          <t>50603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>67088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,74%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17160</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58806</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81519</t>
+          <t>81070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78751</t>
+          <t>79017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103588</t>
+          <t>103844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143783</t>
+          <t>145163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175178</t>
+          <t>177320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102910</t>
+          <t>104067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127203</t>
+          <t>127670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101969</t>
+          <t>100049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127186</t>
+          <t>125636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212823</t>
+          <t>213428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>246183</t>
+          <t>247292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>36096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26718</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>40468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59059</t>
+          <t>58287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>21574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34495</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37407</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50272</t>
+          <t>51102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68155</t>
+          <t>70024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99302</t>
+          <t>98295</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127265</t>
+          <t>126384</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110246</t>
+          <t>110034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139237</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>217769</t>
+          <t>218049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258594</t>
+          <t>258627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162906</t>
+          <t>162873</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154927</t>
+          <t>155316</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>186082</t>
+          <t>185221</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>325838</t>
+          <t>326822</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>367315</t>
+          <t>367572</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>34540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>62300</t>
+          <t>61998</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19644</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19495</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>27781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>41663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97374</t>
+          <t>98653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123120</t>
+          <t>123941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102552</t>
+          <t>102519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129529</t>
+          <t>128324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>208233</t>
+          <t>209000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>245500</t>
+          <t>245670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101989</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128276</t>
+          <t>127066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99524</t>
+          <t>100531</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125456</t>
+          <t>126425</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208400</t>
+          <t>207723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245826</t>
+          <t>245652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27052</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17650</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22201</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40631</t>
+          <t>39483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,69 +7804,69 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4826</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4183</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6945</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2780</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6997</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,14%</t>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>35151</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49651</t>
+          <t>50136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64893</t>
+          <t>65924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87482</t>
+          <t>85560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>56,37%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29550</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44033</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>23961</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>58394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78617</t>
+          <t>78528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140380</t>
+          <t>141120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171105</t>
+          <t>171141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156566</t>
+          <t>155334</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>187166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>307394</t>
+          <t>306581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>350560</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>150512</t>
+          <t>150258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183954</t>
+          <t>180635</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148297</t>
+          <t>148238</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>179901</t>
+          <t>180689</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>306227</t>
+          <t>307059</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>351845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>35710</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A05-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22150</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16864</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27740</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19189</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13980</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14097</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24582</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22150</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16812</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27852</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20325</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14897</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25602</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,21%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26349</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21263</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32428</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20931</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31586</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>52,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20325</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14273</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>26013</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39184</t>
+          <t>39070</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7554</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6136</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6003</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7511</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>630</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2791</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1884</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5137</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4995</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88891</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77163</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>100787</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>82369</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71132</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93594</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>70109</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>93725</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>88891</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>77380</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>101619</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154744</t>
+          <t>154455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188719</t>
+          <t>187664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>122861</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>111015</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>135930</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>51,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>98107</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86298</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>109029</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87664</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>110036</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>122861</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>111036</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>135334</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>51,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201729</t>
+          <t>203869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238959</t>
+          <t>237437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,71%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31587</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,66%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>20867</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14965</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28505</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>14867</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>28222</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,22%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>22985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16723</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>31051</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55432</t>
+          <t>54504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1748,67 +1748,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2774</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6899</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6997</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2546</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5873</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4099</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3981</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3142</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204117</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204117</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204117</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28373</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22439</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34882</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24782</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18341</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31546</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18329</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31085</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>37,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>28373</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34596</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>46,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>44310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60869</t>
+          <t>62280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27699</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21260</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33572</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>37494</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>30797</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>44157</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>30871</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>44201</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>56,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>66,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27699</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>21493</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33690</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56457</t>
+          <t>56070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73986</t>
+          <t>73875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8787</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1517</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8483</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8512</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4323</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8601</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3599</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3631</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2949</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>139413</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>124670</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>153795</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>40,34%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36,07%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>44,5%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>126340</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>111968</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>139968</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>112932</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>140333</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>39,28%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>34,81%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>139413</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>125772</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>154830</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>40,34%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245938</t>
+          <t>246470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>285827</t>
+          <t>286540</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>170885</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>156403</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>185674</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>49,45%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>45,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>53,73%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>161950</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>146931</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>177254</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>148775</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>176045</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>50,35%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>45,68%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>55,11%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>170885</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>156254</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>184719</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>49,45%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>312506</t>
+          <t>312519</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>352604</t>
+          <t>353806</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>30717</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22759</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>38908</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>27341</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>20154</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>36468</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>20016</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>35650</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>30717</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>23180</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>41102</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47508</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71262</t>
+          <t>71925</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -3112,67 +3112,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7845</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>4130</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1393</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8314</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7746</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13538</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3220,72 +3220,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1884</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5623</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321645</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321645</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321645</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12788</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8234</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17827</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13601</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8730</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19656</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19162</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12788</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8195</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18336</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34406</t>
+          <t>33910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25694</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19920</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30830</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>44,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33068</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26971</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38510</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26583</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38536</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,12%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>51,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25694</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20064</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>56,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50603</t>
+          <t>51181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67088</t>
+          <t>67473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2681</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5722</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10949</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10689</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,92%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5463</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2394</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9809</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4020,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3094</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3119</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -4133,107 +4133,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3940</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45205</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45205</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45205</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>52391</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>52391</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>52391</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45205</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45205</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90911</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78452</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>103575</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>69721</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58494</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81070</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>58577</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>82093</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90911</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>79017</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>103844</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,86%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145163</t>
+          <t>143438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177320</t>
+          <t>178091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -4481,67 +4481,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>113982</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>102215</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126784</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>55,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>115760</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>104067</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>127670</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>103727</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>128483</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>56,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>61,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>113982</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>100049</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>125636</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>49,98%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213428</t>
+          <t>213647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247292</t>
+          <t>247492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14745</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9557</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21274</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15253</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9864</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22611</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9752</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21920</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,4%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14745</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9769</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>22160</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39313</t>
+          <t>39084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3826</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1726</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7659</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3528</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7872</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7824</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3826</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7787</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4613</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8800</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1881</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6816</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7022</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4613</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9080</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>12366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>228076</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>228076</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>228076</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206144</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206144</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206144</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>228076</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>228076</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>228076</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20463</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14761</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26352</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29366</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23160</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36096</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35435</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>46,8%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20463</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14715</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26739</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,32%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40468</t>
+          <t>41329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58287</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31433</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25442</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>37996</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>43,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28079</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21574</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34202</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22113</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35175</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>44,75%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>54,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>31433</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25033</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>38166</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>54,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>68155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5094</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2458</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9587</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4671</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9410</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9700</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,45%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,0%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5094</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9010</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -5384,107 +5384,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4613</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>942</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4603</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4312</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4604</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5497,107 +5497,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3537</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3161</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>62743</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>62743</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>62743</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>124162</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>110453</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>137427</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>37,49%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>33,35%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>112687</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>98295</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>126384</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>96921</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>125766</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>35,07%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>30,6%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>39,34%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>124162</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>110034</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>139856</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>37,49%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218049</t>
+          <t>218151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258627</t>
+          <t>257992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>171109</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>154706</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>185195</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>55,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>176908</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>162873</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>192118</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>162847</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>192104</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>55,06%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>59,8%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>171109</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>155316</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>185221</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>326822</t>
+          <t>325681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>367572</t>
+          <t>369009</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25302</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19350</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>34343</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>25646</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>18022</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>34540</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>18517</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>34202</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,98%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>25302</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>18688</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>34212</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>41281</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61998</t>
+          <t>64328</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5374</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2524</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10617</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3528</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7946</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5374</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2414</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>10078</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5267</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2508</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7574</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>5267</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>9887</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>331214</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>331214</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>331214</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321278</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321278</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321278</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>331214</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>331214</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>331214</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6645,67 +6645,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>13642</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8701</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18394</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>12712</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8389</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17323</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8340</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17390</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13642</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8955</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18333</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,87%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>19878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33283</t>
+          <t>33736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19339</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14300</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24362</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>53,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>67,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15010</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10640</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19912</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10699</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20077</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>47,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19339</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14488</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24542</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>53,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27781</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>40653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3041</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6982</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,38%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4092</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8187</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7872</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,86%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>25,73%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3041</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7165</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12516</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36022</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36022</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36022</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36022</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36022</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36022</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>115969</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>103908</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>130559</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>110792</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98653</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>123941</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>96751</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>123847</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>115969</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>102519</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>128324</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209000</t>
+          <t>209534</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>245670</t>
+          <t>246633</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>112960</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>99221</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>125234</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>113939</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>101014</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>127066</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>102027</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>127750</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>45,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>112960</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>100531</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>126425</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207723</t>
+          <t>208662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245652</t>
+          <t>244916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11193</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6359</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16807</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18951</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12124</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26443</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12807</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27083</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,59%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11193</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6852</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17595</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>22363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39483</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4492</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9427</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4747</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9549</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10119</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4492</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1525</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>15529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7779,102 +7779,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4899</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1409</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4579</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4826</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6835</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2780</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6945</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>245985</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>245985</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>245985</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>249838</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>249838</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>249838</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>245985</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>245985</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>245985</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42310</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34974</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49840</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>33313</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>26453</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>40762</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26470</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>40211</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>44,78%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42310</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>35151</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>50136</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65924</t>
+          <t>65154</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85560</t>
+          <t>86337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31869</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>24416</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38914</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,55%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>36662</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>29114</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>43996</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>29538</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>43621</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>49,28%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>59,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>31869</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>23961</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>39151</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>57755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78528</t>
+          <t>79053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6916</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3717</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7659</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7480</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3212</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1166</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7095</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -8343,107 +8343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>706</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3544</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>77391</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>77391</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>77391</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>77391</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>77391</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>77391</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>171921</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>155628</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>188894</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>47,84%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>52,56%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>156817</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>141120</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>171141</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>142511</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>171334</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>44,04%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>39,63%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>48,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>171921</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>155334</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>187166</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>47,84%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>306581</t>
+          <t>305925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>350560</t>
+          <t>351166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>164169</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>147922</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>180723</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45,68%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>165611</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>150258</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>180635</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>150373</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>180935</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>46,51%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>42,2%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>50,73%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>164169</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>148238</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>180689</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>45,68%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>307059</t>
+          <t>306763</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>351845</t>
+          <t>351643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>17446</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11890</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>25543</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>26760</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>19242</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>19361</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>36530</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>17446</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>11357</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>25410</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35039</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56341</t>
+          <t>56158</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4492</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1597</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9298</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>5453</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>10864</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10899</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4492</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1642</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>9849</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -9143,69 +9143,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4769</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>1409</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4249</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>359398</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>359398</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>359398</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>356050</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>356050</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>356050</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>359398</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>359398</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>359398</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
